--- a/artfynd/A 60901-2021 artfynd.xlsx
+++ b/artfynd/A 60901-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60901-2021 artfynd.xlsx
+++ b/artfynd/A 60901-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2077,1290 +2077,6 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>112605228</v>
-      </c>
-      <c r="B14" t="n">
-        <v>81593</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>718058</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7158257</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>112605226</v>
-      </c>
-      <c r="B15" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>718052</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7158359</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>112605229</v>
-      </c>
-      <c r="B16" t="n">
-        <v>77891</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>185</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Bryoria nadvornikiana</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>718065</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7158253</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>112605233</v>
-      </c>
-      <c r="B17" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>718094</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7158215</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>112605236</v>
-      </c>
-      <c r="B18" t="n">
-        <v>78448</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>718063</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7158168</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>112605234</v>
-      </c>
-      <c r="B19" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>718063</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7158183</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>112605227</v>
-      </c>
-      <c r="B20" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>718054</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7158272</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>112605225</v>
-      </c>
-      <c r="B21" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>718047</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7158398</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>112605230</v>
-      </c>
-      <c r="B22" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>718083</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7158249</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>112605231</v>
-      </c>
-      <c r="B23" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>718122</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7158239</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>112605224</v>
-      </c>
-      <c r="B24" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>718067</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7158257</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>112605232</v>
-      </c>
-      <c r="B25" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Slipstensjön, Vb</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>718112</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7158219</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
